--- a/data/Equipments.xlsx
+++ b/data/Equipments.xlsx
@@ -425,31 +425,31 @@
         <v>攻击力</v>
       </c>
       <c r="I1" t="str">
+        <v>防御力</v>
+      </c>
+      <c r="J1" t="str">
+        <v>生命值</v>
+      </c>
+      <c r="K1" t="str">
         <v>暴击率</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>暴击伤害</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>吸血比例</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>闪避值</v>
+      </c>
+      <c r="O1" t="str">
         <v>特殊效果</v>
       </c>
-      <c r="M1" t="str">
-        <v>防御力</v>
-      </c>
-      <c r="N1" t="str">
-        <v>生命值</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>隐身概率</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>隐身时长(秒)</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>闪避值</v>
       </c>
       <c r="R1" t="str">
         <v>击杀回血</v>
@@ -466,7 +466,7 @@
         <v>sword_1</v>
       </c>
       <c r="C2" t="str">
-        <v>新手剑</v>
+        <v>铜锈短匕</v>
       </c>
       <c r="D2" t="str">
         <v>weapon</v>
@@ -475,7 +475,7 @@
         <v>N</v>
       </c>
       <c r="F2" t="str">
-        <v>一把普通的剑，适合初学者</v>
+        <v>一件青铜碎片的灵凝结成刃——它不够锋利，但足够带你跨过第一条灵脉</v>
       </c>
       <c r="G2" t="str">
         <v>🗡️</v>
@@ -492,7 +492,7 @@
         <v>sword_2</v>
       </c>
       <c r="C3" t="str">
-        <v>锋利之刃</v>
+        <v>战国剑·淬火</v>
       </c>
       <c r="D3" t="str">
         <v>weapon</v>
@@ -501,7 +501,7 @@
         <v>R</v>
       </c>
       <c r="F3" t="str">
-        <v>锋利的剑刃，切割如风</v>
+        <v>战国剑的灵刃——两千年前的淬火还在剑锋上跳动</v>
       </c>
       <c r="G3" t="str">
         <v>⚔️</v>
@@ -509,7 +509,7 @@
       <c r="H3">
         <v>15</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>2</v>
       </c>
     </row>
@@ -521,7 +521,7 @@
         <v>staff_1</v>
       </c>
       <c r="C4" t="str">
-        <v>魔法杖</v>
+        <v>竹简卷</v>
       </c>
       <c r="D4" t="str">
         <v>weapon</v>
@@ -530,7 +530,7 @@
         <v>R</v>
       </c>
       <c r="F4" t="str">
-        <v>蕴含魔力的法杖</v>
+        <v>一卷战国竹简的灵——展开的不只是文字，还有两千年前的呼吸</v>
       </c>
       <c r="G4" t="str">
         <v>🪄</v>
@@ -538,7 +538,7 @@
       <c r="H4">
         <v>10</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>0.1</v>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>ice_staff</v>
       </c>
       <c r="C5" t="str">
-        <v>冰晶法杖</v>
+        <v>青花杖</v>
       </c>
       <c r="D5" t="str">
         <v>weapon</v>
@@ -559,15 +559,15 @@
         <v>R</v>
       </c>
       <c r="F5" t="str">
-        <v>由冰晶凝聚而成，寒气逼人</v>
+        <v>元代青花瓷瓶的残片凝成——杖头是那朵没画完的牡丹</v>
       </c>
       <c r="G5" t="str">
-        <v>❄️</v>
+        <v>💧</v>
       </c>
       <c r="H5">
         <v>12</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>3</v>
       </c>
     </row>
@@ -579,7 +579,7 @@
         <v>fire_sword</v>
       </c>
       <c r="C6" t="str">
-        <v>火焰长剑</v>
+        <v>鼎纹剑</v>
       </c>
       <c r="D6" t="str">
         <v>weapon</v>
@@ -588,7 +588,7 @@
         <v>R</v>
       </c>
       <c r="F6" t="str">
-        <v>剑身燃烧着永恒的火焰</v>
+        <v>青铜鼎纹从鼎身剥离后自己卷成了剑——剑锋上是商代的饕餮纹</v>
       </c>
       <c r="G6" t="str">
         <v>🔥</v>
@@ -596,7 +596,7 @@
       <c r="H6">
         <v>18</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>0.05</v>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <v>sword_3</v>
       </c>
       <c r="C7" t="str">
-        <v>星之剑</v>
+        <v>玉琮剑</v>
       </c>
       <c r="D7" t="str">
         <v>weapon</v>
@@ -617,7 +617,7 @@
         <v>SR</v>
       </c>
       <c r="F7" t="str">
-        <v>由星光凝聚而成的剑</v>
+        <v>良渚玉琮的灵凝成长剑——四方的剑身，每一面都是玉的白</v>
       </c>
       <c r="G7" t="str">
         <v>✨</v>
@@ -625,10 +625,10 @@
       <c r="H7">
         <v>30</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>5</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>0.2</v>
       </c>
     </row>
@@ -640,7 +640,7 @@
         <v>meteor_blade</v>
       </c>
       <c r="C8" t="str">
-        <v>流星刃</v>
+        <v>铁饼之刃</v>
       </c>
       <c r="D8" t="str">
         <v>weapon</v>
@@ -649,7 +649,7 @@
         <v>SR</v>
       </c>
       <c r="F8" t="str">
-        <v>宛如流星划过夜空</v>
+        <v>掷铁饼者手中的那枚石饼——在灵域中它被打成了刃</v>
       </c>
       <c r="G8" t="str">
         <v>🌠</v>
@@ -657,10 +657,10 @@
       <c r="H8">
         <v>35</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>8</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>0.15</v>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>frost_scepter</v>
       </c>
       <c r="C9" t="str">
-        <v>冰霜权杖</v>
+        <v>金缮杖</v>
       </c>
       <c r="D9" t="str">
         <v>weapon</v>
@@ -681,7 +681,7 @@
         <v>SR</v>
       </c>
       <c r="F9" t="str">
-        <v>极寒之地的神器</v>
+        <v>金缮修复过的茶碗灵——杖身上的金丝裂痕是它曾经碎过的证据</v>
       </c>
       <c r="G9" t="str">
         <v>💠</v>
@@ -689,7 +689,7 @@
       <c r="H9">
         <v>25</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>10</v>
       </c>
     </row>
@@ -701,7 +701,7 @@
         <v>blaze_edge</v>
       </c>
       <c r="C10" t="str">
-        <v>烈焰剑</v>
+        <v>太阳石剑</v>
       </c>
       <c r="D10" t="str">
         <v>weapon</v>
@@ -710,7 +710,7 @@
         <v>SR</v>
       </c>
       <c r="F10" t="str">
-        <v>燃烧一切的炽热之剑</v>
+        <v>太阳石刻纹中抽出来的光——不是火焰，是末日预言在燃烧</v>
       </c>
       <c r="G10" t="str">
         <v>💥</v>
@@ -718,7 +718,7 @@
       <c r="H10">
         <v>40</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>0.25</v>
       </c>
     </row>
@@ -730,7 +730,7 @@
         <v>star_sword</v>
       </c>
       <c r="C11" t="str">
-        <v>星辰圣剑</v>
+        <v>编钟剑</v>
       </c>
       <c r="D11" t="str">
         <v>weapon</v>
@@ -739,7 +739,7 @@
         <v>SSR</v>
       </c>
       <c r="F11" t="str">
-        <v>凝聚万千星辰之力</v>
+        <v>曾侯乙编钟的灵凝成一剑——每次挥动，都有一段音节在邪灵身上炸开</v>
       </c>
       <c r="G11" t="str">
         <v>🌟</v>
@@ -747,10 +747,10 @@
       <c r="H11">
         <v>60</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>12</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>0.3</v>
       </c>
     </row>
@@ -762,7 +762,7 @@
         <v>heart_of_ice</v>
       </c>
       <c r="C12" t="str">
-        <v>极寒之心</v>
+        <v>北欧角杯</v>
       </c>
       <c r="D12" t="str">
         <v>weapon</v>
@@ -771,18 +771,18 @@
         <v>SSR</v>
       </c>
       <c r="F12" t="str">
-        <v>永冻之心的碎片</v>
+        <v>维京金角中的灵凝聚成器——金角唤来的不是英灵，是千年的冰霜</v>
       </c>
       <c r="G12" t="str">
-        <v>💎</v>
+        <v>🪨</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>15</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>0.2</v>
       </c>
     </row>
@@ -794,7 +794,7 @@
         <v>emperor_flame</v>
       </c>
       <c r="C13" t="str">
-        <v>炎帝之刃</v>
+        <v>法老刃</v>
       </c>
       <c r="D13" t="str">
         <v>weapon</v>
@@ -803,7 +803,7 @@
         <v>SSR</v>
       </c>
       <c r="F13" t="str">
-        <v>炎帝遗留的神器</v>
+        <v>法老金棺上的圣甲虫纹从棺盖剥落，卷成了一柄刃</v>
       </c>
       <c r="G13" t="str">
         <v>🔥</v>
@@ -811,7 +811,7 @@
       <c r="H13">
         <v>70</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>0.4</v>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>devourer_blade</v>
       </c>
       <c r="C14" t="str">
-        <v>吞噬之刃</v>
+        <v>罗塞塔刃</v>
       </c>
       <c r="D14" t="str">
         <v>weapon</v>
@@ -832,7 +832,7 @@
         <v>SSR</v>
       </c>
       <c r="F14" t="str">
-        <v>击杀怪物回复1%血量</v>
+        <v>罗塞塔石碑的碎片之灵凝聚为刃——它吞噬的不只是灵能，还有邪灵的技能</v>
       </c>
       <c r="G14" t="str">
         <v>🗡️</v>
@@ -840,13 +840,13 @@
       <c r="H14">
         <v>55</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>10</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>0.01</v>
       </c>
-      <c r="L14" t="str">
+      <c r="O14" t="str">
         <v>lifesteal</v>
       </c>
     </row>
@@ -858,7 +858,7 @@
         <v>galaxy_blade</v>
       </c>
       <c r="C15" t="str">
-        <v>星河神剑</v>
+        <v>万灵剑</v>
       </c>
       <c r="D15" t="str">
         <v>weapon</v>
@@ -867,7 +867,7 @@
         <v>UR</v>
       </c>
       <c r="F15" t="str">
-        <v>跨越星河的终极之剑</v>
+        <v>第一百次融合的产物——剑上有八种文明的纹路互相缠绕，没有一种覆盖了另一种</v>
       </c>
       <c r="G15" t="str">
         <v>⚔️</v>
@@ -875,10 +875,10 @@
       <c r="H15">
         <v>100</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>20</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>0.5</v>
       </c>
     </row>
@@ -890,7 +890,7 @@
         <v>armor_1</v>
       </c>
       <c r="C16" t="str">
-        <v>布衣</v>
+        <v>棉布小褂</v>
       </c>
       <c r="D16" t="str">
         <v>armor</v>
@@ -899,15 +899,15 @@
         <v>N</v>
       </c>
       <c r="F16" t="str">
-        <v>简单的布衣，聊胜于无</v>
+        <v>蜀汉城市井中的一件素棉衣——没有千年历史，但有你的体温</v>
       </c>
       <c r="G16" t="str">
         <v>👕</v>
       </c>
-      <c r="M16">
+      <c r="I16">
         <v>5</v>
       </c>
-      <c r="N16">
+      <c r="J16">
         <v>20</v>
       </c>
     </row>
@@ -919,7 +919,7 @@
         <v>armor_2</v>
       </c>
       <c r="C17" t="str">
-        <v>铁甲</v>
+        <v>战国铁胄</v>
       </c>
       <c r="D17" t="str">
         <v>armor</v>
@@ -928,15 +928,15 @@
         <v>R</v>
       </c>
       <c r="F17" t="str">
-        <v>坚固的铁甲</v>
+        <v>战国铁胄之灵——两千年的锈迹凝成了防御层</v>
       </c>
       <c r="G17" t="str">
         <v>🛡️</v>
       </c>
-      <c r="M17">
+      <c r="I17">
         <v>15</v>
       </c>
-      <c r="N17">
+      <c r="J17">
         <v>50</v>
       </c>
     </row>
@@ -948,7 +948,7 @@
         <v>ice_robe</v>
       </c>
       <c r="C18" t="str">
-        <v>冰丝长袍</v>
+        <v>冰纨袍</v>
       </c>
       <c r="D18" t="str">
         <v>armor</v>
@@ -957,19 +957,19 @@
         <v>R</v>
       </c>
       <c r="F18" t="str">
-        <v>由冰蚕丝织成的长袍</v>
+        <v>汉代冰纨织物的灵——不是冰做的，是在冰窖里睡了一千年</v>
       </c>
       <c r="G18" t="str">
         <v>🧥</v>
       </c>
       <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>60</v>
+      </c>
+      <c r="K18">
         <v>2</v>
-      </c>
-      <c r="M18">
-        <v>10</v>
-      </c>
-      <c r="N18">
-        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -980,7 +980,7 @@
         <v>flame_cloak</v>
       </c>
       <c r="C19" t="str">
-        <v>火焰披风</v>
+        <v>冶炼披风</v>
       </c>
       <c r="D19" t="str">
         <v>armor</v>
@@ -989,19 +989,19 @@
         <v>R</v>
       </c>
       <c r="F19" t="str">
-        <v>永不熄灭的火焰披风</v>
+        <v>侯马铸铜遗址的炉火之灵——两千年前的烈火从不脱工作</v>
       </c>
       <c r="G19" t="str">
         <v>🔥</v>
       </c>
+      <c r="I19">
+        <v>12</v>
+      </c>
       <c r="J19">
+        <v>40</v>
+      </c>
+      <c r="L19">
         <v>0.05</v>
-      </c>
-      <c r="M19">
-        <v>12</v>
-      </c>
-      <c r="N19">
-        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1012,7 +1012,7 @@
         <v>armor_3</v>
       </c>
       <c r="C20" t="str">
-        <v>星辉战甲</v>
+        <v>璎珞甲</v>
       </c>
       <c r="D20" t="str">
         <v>armor</v>
@@ -1021,19 +1021,19 @@
         <v>SR</v>
       </c>
       <c r="F20" t="str">
-        <v>闪耀星光的战甲</v>
+        <v>佛像上的璎珞珠串之灵编织成甲——每一颗珠子都有它自己的梵音</v>
       </c>
       <c r="G20" t="str">
         <v>🎖️</v>
       </c>
       <c r="I20">
+        <v>30</v>
+      </c>
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
         <v>3</v>
-      </c>
-      <c r="M20">
-        <v>30</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -1044,7 +1044,7 @@
         <v>ice_crystal_armor</v>
       </c>
       <c r="C21" t="str">
-        <v>冰晶铠甲</v>
+        <v>冰鉴铠</v>
       </c>
       <c r="D21" t="str">
         <v>armor</v>
@@ -1053,19 +1053,19 @@
         <v>SR</v>
       </c>
       <c r="F21" t="str">
-        <v>由千年冰晶打造</v>
+        <v>战国冰鉴的灵——冷藏了两千年的护体灵光</v>
       </c>
       <c r="G21" t="str">
-        <v>❄️</v>
+        <v>💧</v>
       </c>
       <c r="I21">
+        <v>35</v>
+      </c>
+      <c r="J21">
+        <v>80</v>
+      </c>
+      <c r="K21">
         <v>5</v>
-      </c>
-      <c r="M21">
-        <v>35</v>
-      </c>
-      <c r="N21">
-        <v>80</v>
       </c>
     </row>
     <row r="22">
@@ -1076,7 +1076,7 @@
         <v>lava_armor</v>
       </c>
       <c r="C22" t="str">
-        <v>熔岩战甲</v>
+        <v>铜造像甲</v>
       </c>
       <c r="D22" t="str">
         <v>armor</v>
@@ -1085,19 +1085,19 @@
         <v>SR</v>
       </c>
       <c r="F22" t="str">
-        <v>在地心熔岩中锻造</v>
+        <v>贝宁青铜头像延展而成的甲——大地最古老的防御形态</v>
       </c>
       <c r="G22" t="str">
         <v>🌋</v>
       </c>
+      <c r="I22">
+        <v>40</v>
+      </c>
       <c r="J22">
+        <v>120</v>
+      </c>
+      <c r="L22">
         <v>0.1</v>
-      </c>
-      <c r="M22">
-        <v>40</v>
-      </c>
-      <c r="N22">
-        <v>120</v>
       </c>
     </row>
     <row r="23">
@@ -1108,7 +1108,7 @@
         <v>star_armor</v>
       </c>
       <c r="C23" t="str">
-        <v>星辰战甲</v>
+        <v>万国甲</v>
       </c>
       <c r="D23" t="str">
         <v>armor</v>
@@ -1117,19 +1117,19 @@
         <v>SSR</v>
       </c>
       <c r="F23" t="str">
-        <v>星光编织的神甲</v>
+        <v>集齐四座灵域文明锻造的甲——不同纹样在甲面上各自呼吸</v>
       </c>
       <c r="G23" t="str">
         <v>🌟</v>
       </c>
       <c r="I23">
+        <v>50</v>
+      </c>
+      <c r="J23">
+        <v>150</v>
+      </c>
+      <c r="K23">
         <v>8</v>
-      </c>
-      <c r="M23">
-        <v>50</v>
-      </c>
-      <c r="N23">
-        <v>150</v>
       </c>
     </row>
     <row r="24">
@@ -1140,7 +1140,7 @@
         <v>permafrost_armor</v>
       </c>
       <c r="C24" t="str">
-        <v>永冻之铠</v>
+        <v>维京船甲</v>
       </c>
       <c r="D24" t="str">
         <v>armor</v>
@@ -1149,22 +1149,22 @@
         <v>SSR</v>
       </c>
       <c r="F24" t="str">
-        <v>永恒冻土的力量</v>
+        <v>维京长船上的橡木之灵——冰冷不是北方的诅咒，是它的铠甲</v>
       </c>
       <c r="G24" t="str">
         <v>💠</v>
       </c>
       <c r="I24">
+        <v>55</v>
+      </c>
+      <c r="J24">
+        <v>130</v>
+      </c>
+      <c r="K24">
         <v>10</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>0.15</v>
-      </c>
-      <c r="M24">
-        <v>55</v>
-      </c>
-      <c r="N24">
-        <v>130</v>
       </c>
     </row>
     <row r="25">
@@ -1175,7 +1175,7 @@
         <v>emperor_armor</v>
       </c>
       <c r="C25" t="str">
-        <v>炎帝战甲</v>
+        <v>祭祀甲</v>
       </c>
       <c r="D25" t="str">
         <v>armor</v>
@@ -1184,19 +1184,19 @@
         <v>SSR</v>
       </c>
       <c r="F25" t="str">
-        <v>炎帝的战甲，抵御一切</v>
+        <v>玛雅祭坛石的灵——它的防御是让攻击在时间中弥散</v>
       </c>
       <c r="G25" t="str">
         <v>🔥</v>
       </c>
+      <c r="I25">
+        <v>60</v>
+      </c>
       <c r="J25">
+        <v>180</v>
+      </c>
+      <c r="L25">
         <v>0.2</v>
-      </c>
-      <c r="M25">
-        <v>60</v>
-      </c>
-      <c r="N25">
-        <v>180</v>
       </c>
     </row>
     <row r="26">
@@ -1207,7 +1207,7 @@
         <v>void_armor</v>
       </c>
       <c r="C26" t="str">
-        <v>虚空战甲</v>
+        <v>隐灵甲</v>
       </c>
       <c r="D26" t="str">
         <v>armor</v>
@@ -1216,24 +1216,24 @@
         <v>SSR</v>
       </c>
       <c r="F26" t="str">
-        <v>被攻击时15%概率隐身1秒</v>
+        <v>浮世绘中的隐世之灵——邪灵看不见你时才会显形</v>
       </c>
       <c r="G26" t="str">
         <v>🌀</v>
       </c>
-      <c r="L26" t="str">
+      <c r="I26">
+        <v>45</v>
+      </c>
+      <c r="J26">
+        <v>120</v>
+      </c>
+      <c r="O26" t="str">
         <v>vanish</v>
       </c>
-      <c r="M26">
-        <v>45</v>
-      </c>
-      <c r="N26">
-        <v>120</v>
-      </c>
-      <c r="O26">
+      <c r="P26">
         <v>0.15</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>1</v>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
         <v>galaxy_armor</v>
       </c>
       <c r="C27" t="str">
-        <v>星河圣甲</v>
+        <v>大地母甲</v>
       </c>
       <c r="D27" t="str">
         <v>armor</v>
@@ -1254,22 +1254,22 @@
         <v>UR</v>
       </c>
       <c r="F27" t="str">
-        <v>星河之力护佑全身</v>
+        <v>非洲大地母神像的碎片之灵淬成的甲——她承受过七层污染</v>
       </c>
       <c r="G27" t="str">
         <v>✨</v>
       </c>
       <c r="I27">
+        <v>80</v>
+      </c>
+      <c r="J27">
+        <v>250</v>
+      </c>
+      <c r="K27">
         <v>15</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>0.25</v>
-      </c>
-      <c r="M27">
-        <v>80</v>
-      </c>
-      <c r="N27">
-        <v>250</v>
       </c>
     </row>
     <row r="28">
@@ -1280,7 +1280,7 @@
         <v>ring_1</v>
       </c>
       <c r="C28" t="str">
-        <v>铜戒指</v>
+        <v>铜雀戒</v>
       </c>
       <c r="D28" t="str">
         <v>accessory</v>
@@ -1289,12 +1289,12 @@
         <v>N</v>
       </c>
       <c r="F28" t="str">
-        <v>普通的戒指</v>
+        <v>青铜雀形小件之灵——戴在手上轻若无物，但它确实是三千年前那只雀</v>
       </c>
       <c r="G28" t="str">
         <v>💍</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>1</v>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         <v>ring_2</v>
       </c>
       <c r="C29" t="str">
-        <v>暴击戒指</v>
+        <v>蝉翼戒</v>
       </c>
       <c r="D29" t="str">
         <v>accessory</v>
@@ -1315,15 +1315,15 @@
         <v>R</v>
       </c>
       <c r="F29" t="str">
-        <v>增加暴击能力的戒指</v>
+        <v>玉蝉仙翅膀边缘的一丝灵凝聚成的戒指——你能感受到它振翅的频率</v>
       </c>
       <c r="G29" t="str">
-        <v>💎</v>
-      </c>
-      <c r="I29">
+        <v>🪨</v>
+      </c>
+      <c r="K29">
         <v>5</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>0.15</v>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
         <v>ice_earring</v>
       </c>
       <c r="C30" t="str">
-        <v>冰晶耳环</v>
+        <v>莲花耳坠</v>
       </c>
       <c r="D30" t="str">
         <v>accessory</v>
@@ -1344,15 +1344,15 @@
         <v>R</v>
       </c>
       <c r="F30" t="str">
-        <v>冰晶打造的耳环</v>
+        <v>曼陀罗灵域中莲花池的凝结——整个池子挂在耳边</v>
       </c>
       <c r="G30" t="str">
-        <v>❄️</v>
-      </c>
-      <c r="I30">
+        <v>💧</v>
+      </c>
+      <c r="K30">
         <v>4</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>0.1</v>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         <v>fire_amulet</v>
       </c>
       <c r="C31" t="str">
-        <v>火焰护符</v>
+        <v>日石护符</v>
       </c>
       <c r="D31" t="str">
         <v>accessory</v>
@@ -1373,7 +1373,7 @@
         <v>R</v>
       </c>
       <c r="F31" t="str">
-        <v>蕴含火焰之力的护符</v>
+        <v>太阳石边缘剥落的一小片石灵——挂在你脖子上燃烧</v>
       </c>
       <c r="G31" t="str">
         <v>🔥</v>
@@ -1381,7 +1381,7 @@
       <c r="H31">
         <v>8</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>0.1</v>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         <v>necklace_1</v>
       </c>
       <c r="C32" t="str">
-        <v>星源项链</v>
+        <v>玺印项链</v>
       </c>
       <c r="D32" t="str">
         <v>accessory</v>
@@ -1402,7 +1402,7 @@
         <v>SR</v>
       </c>
       <c r="F32" t="str">
-        <v>蕴含星源之力的项链</v>
+        <v>传国玉玺的残灵——方寸之间，千年之重</v>
       </c>
       <c r="G32" t="str">
         <v>📿</v>
@@ -1410,10 +1410,10 @@
       <c r="H32">
         <v>10</v>
       </c>
-      <c r="I32">
+      <c r="K32">
         <v>8</v>
       </c>
-      <c r="J32">
+      <c r="L32">
         <v>0.25</v>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
         <v>frost_pendant</v>
       </c>
       <c r="C33" t="str">
-        <v>冰霜吊坠</v>
+        <v>极光吊坠</v>
       </c>
       <c r="D33" t="str">
         <v>accessory</v>
@@ -1434,15 +1434,15 @@
         <v>SR</v>
       </c>
       <c r="F33" t="str">
-        <v>永冬之地的珍宝</v>
+        <v>北极光凝聚成的吊坠——不是冻结的，是等待的</v>
       </c>
       <c r="G33" t="str">
         <v>💠</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>12</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>0.2</v>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
         <v>blaze_badge</v>
       </c>
       <c r="C34" t="str">
-        <v>烈焰徽章</v>
+        <v>历法徽章</v>
       </c>
       <c r="D34" t="str">
         <v>accessory</v>
@@ -1463,7 +1463,7 @@
         <v>SR</v>
       </c>
       <c r="F34" t="str">
-        <v>烈焰骑士的荣耀</v>
+        <v>玛雅历法盘的一格——每一格都是对时间的精准计量</v>
       </c>
       <c r="G34" t="str">
         <v>🔥</v>
@@ -1471,7 +1471,7 @@
       <c r="H34">
         <v>15</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>0.3</v>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
         <v>star_eye</v>
       </c>
       <c r="C35" t="str">
-        <v>星辰之眼</v>
+        <v>荷鲁斯之眼</v>
       </c>
       <c r="D35" t="str">
         <v>accessory</v>
@@ -1492,7 +1492,7 @@
         <v>SSR</v>
       </c>
       <c r="F35" t="str">
-        <v>洞察星辰的神器</v>
+        <v>埃及天空之神荷鲁斯的灵——你看不见的紊乱，它替你看见</v>
       </c>
       <c r="G35" t="str">
         <v>👁️</v>
@@ -1500,10 +1500,10 @@
       <c r="H35">
         <v>20</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>15</v>
       </c>
-      <c r="J35">
+      <c r="L35">
         <v>0.35</v>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         <v>aurora_crown</v>
       </c>
       <c r="C36" t="str">
-        <v>极光之冠</v>
+        <v>王冠·奥西里斯</v>
       </c>
       <c r="D36" t="str">
         <v>accessory</v>
@@ -1524,15 +1524,15 @@
         <v>SSR</v>
       </c>
       <c r="F36" t="str">
-        <v>北极光的化身</v>
+        <v>奥西里斯之冠的灵碎片——重生是被杀过才能拥有的力量</v>
       </c>
       <c r="G36" t="str">
         <v>👑</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>20</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>0.4</v>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         <v>emperor_ring</v>
       </c>
       <c r="C37" t="str">
-        <v>炎皇之戒</v>
+        <v>金棺指环</v>
       </c>
       <c r="D37" t="str">
         <v>accessory</v>
@@ -1553,7 +1553,7 @@
         <v>SSR</v>
       </c>
       <c r="F37" t="str">
-        <v>炎皇的权戒</v>
+        <v>法老金棺上的金属纹饰圈——凋零是最执着的羁绊</v>
       </c>
       <c r="G37" t="str">
         <v>💍</v>
@@ -1561,7 +1561,7 @@
       <c r="H37">
         <v>25</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>0.5</v>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
         <v>abyss_pendant</v>
       </c>
       <c r="C38" t="str">
-        <v>深渊吊坠</v>
+        <v>灵脉吊坠</v>
       </c>
       <c r="D38" t="str">
         <v>accessory</v>
@@ -1582,18 +1582,18 @@
         <v>SSR</v>
       </c>
       <c r="F38" t="str">
-        <v>深渊的馈赠，暴击与闪避兼备</v>
+        <v>灵脉交叉处凝固的能量结晶——暴击和闪避不是技巧，是灵在你身上留的位置</v>
       </c>
       <c r="G38" t="str">
         <v>💠</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>18</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>0.4</v>
       </c>
-      <c r="Q38">
+      <c r="N38">
         <v>5</v>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         <v>galaxy_heart</v>
       </c>
       <c r="C39" t="str">
-        <v>星河之心</v>
+        <v>万灵之心</v>
       </c>
       <c r="D39" t="str">
         <v>accessory</v>
@@ -1614,7 +1614,7 @@
         <v>UR</v>
       </c>
       <c r="F39" t="str">
-        <v>星河的核心，蕴含无限力量</v>
+        <v>八座灵域在一次短暂共振中共同凝出的一颗结晶——没有任何单一文明可以在上面签名</v>
       </c>
       <c r="G39" t="str">
         <v>💜</v>
@@ -1622,10 +1622,10 @@
       <c r="H39">
         <v>30</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>25</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>0.6</v>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>frost_set</v>
       </c>
       <c r="C40" t="str">
-        <v>冰霜套装</v>
+        <v>水行套装</v>
       </c>
       <c r="D40" t="str">
         <v>set</v>
@@ -1646,25 +1646,25 @@
         <v>SR</v>
       </c>
       <c r="F40" t="str">
-        <v>冰霜之力集结套装</v>
+        <v>水行之力集结——五件器物共鸣时，水灵光走向你比走向邪灵更近</v>
       </c>
       <c r="G40" t="str">
-        <v>❄️</v>
+        <v>💠</v>
       </c>
       <c r="H40">
         <v>15</v>
       </c>
       <c r="I40">
+        <v>15</v>
+      </c>
+      <c r="J40">
+        <v>60</v>
+      </c>
+      <c r="K40">
         <v>8</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>0.2</v>
-      </c>
-      <c r="M40">
-        <v>15</v>
-      </c>
-      <c r="N40">
-        <v>60</v>
       </c>
     </row>
     <row r="41">
@@ -1675,7 +1675,7 @@
         <v>blaze_set</v>
       </c>
       <c r="C41" t="str">
-        <v>烈焰套装</v>
+        <v>火行套装</v>
       </c>
       <c r="D41" t="str">
         <v>set</v>
@@ -1684,7 +1684,7 @@
         <v>SR</v>
       </c>
       <c r="F41" t="str">
-        <v>烈焰之力集结套装</v>
+        <v>火行之力集结——温度不是创伤，是灵在煮沸紊乱</v>
       </c>
       <c r="G41" t="str">
         <v>🔥</v>
@@ -1692,14 +1692,14 @@
       <c r="H41">
         <v>25</v>
       </c>
+      <c r="I41">
+        <v>10</v>
+      </c>
       <c r="J41">
+        <v>40</v>
+      </c>
+      <c r="L41">
         <v>0.25</v>
-      </c>
-      <c r="M41">
-        <v>10</v>
-      </c>
-      <c r="N41">
-        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1710,7 +1710,7 @@
         <v>set_1</v>
       </c>
       <c r="C42" t="str">
-        <v>星之套装</v>
+        <v>灵域入门套装</v>
       </c>
       <c r="D42" t="str">
         <v>set</v>
@@ -1719,7 +1719,7 @@
         <v>SSR</v>
       </c>
       <c r="F42" t="str">
-        <v>传说中的星之战士套装</v>
+        <v>进入第一座灵域的纪念——每一件器物都来自同一道灵脉</v>
       </c>
       <c r="G42" t="str">
         <v>⭐</v>
@@ -1728,16 +1728,16 @@
         <v>20</v>
       </c>
       <c r="I42">
+        <v>20</v>
+      </c>
+      <c r="J42">
+        <v>80</v>
+      </c>
+      <c r="K42">
         <v>10</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>0.3</v>
-      </c>
-      <c r="M42">
-        <v>20</v>
-      </c>
-      <c r="N42">
-        <v>80</v>
       </c>
     </row>
     <row r="43">
@@ -1748,7 +1748,7 @@
         <v>star_set</v>
       </c>
       <c r="C43" t="str">
-        <v>星辰套装</v>
+        <v>唤灵套装</v>
       </c>
       <c r="D43" t="str">
         <v>set</v>
@@ -1757,7 +1757,7 @@
         <v>SSR</v>
       </c>
       <c r="F43" t="str">
-        <v>星辰之力完全体</v>
+        <v>跨越四座灵域时分别得到的四件灵器——每一件都是不同文明的一句"你可以继续走"</v>
       </c>
       <c r="G43" t="str">
         <v>🌟</v>
@@ -1766,16 +1766,16 @@
         <v>30</v>
       </c>
       <c r="I43">
+        <v>25</v>
+      </c>
+      <c r="J43">
+        <v>100</v>
+      </c>
+      <c r="K43">
         <v>12</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>0.35</v>
-      </c>
-      <c r="M43">
-        <v>25</v>
-      </c>
-      <c r="N43">
-        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -1786,7 +1786,7 @@
         <v>galaxy_set</v>
       </c>
       <c r="C44" t="str">
-        <v>星河套装</v>
+        <v>八灵套装</v>
       </c>
       <c r="D44" t="str">
         <v>set</v>
@@ -1795,25 +1795,25 @@
         <v>UR</v>
       </c>
       <c r="F44" t="str">
-        <v>跨越星河的终极套装</v>
+        <v>八座灵域各出一件灵器——穿上它的瞬间你就能听到所有文明的灵脉在同一时刻呼吸</v>
       </c>
       <c r="G44" t="str">
-        <v>🌌</v>
+        <v>🔮</v>
       </c>
       <c r="H44">
         <v>50</v>
       </c>
       <c r="I44">
+        <v>40</v>
+      </c>
+      <c r="J44">
+        <v>150</v>
+      </c>
+      <c r="K44">
         <v>20</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>0.5</v>
-      </c>
-      <c r="M44">
-        <v>40</v>
-      </c>
-      <c r="N44">
-        <v>150</v>
       </c>
     </row>
     <row r="45">
@@ -1824,7 +1824,7 @@
         <v>devourer_crown</v>
       </c>
       <c r="C45" t="str">
-        <v>吞噬者之冠</v>
+        <v>唤灵冠</v>
       </c>
       <c r="D45" t="str">
         <v>set</v>
@@ -1833,7 +1833,7 @@
         <v>UR</v>
       </c>
       <c r="F45" t="str">
-        <v>全属性+25%，击杀怪物回复3HP</v>
+        <v>唤灵人的最终证明——来自八座灵域各一缕灵脉的馈赠。不是吞噬，是融汇</v>
       </c>
       <c r="G45" t="str">
         <v>👑</v>
@@ -1844,14 +1844,14 @@
       <c r="I45">
         <v>25</v>
       </c>
-      <c r="J45">
+      <c r="K45">
+        <v>25</v>
+      </c>
+      <c r="L45">
         <v>0.25</v>
       </c>
-      <c r="L45" t="str">
+      <c r="O45" t="str">
         <v>devourer_set</v>
-      </c>
-      <c r="M45">
-        <v>25</v>
       </c>
       <c r="R45">
         <v>3</v>
@@ -1865,7 +1865,7 @@
         <v>thief_blade</v>
       </c>
       <c r="C46" t="str">
-        <v>偷星之刃</v>
+        <v>窃灵之刃</v>
       </c>
       <c r="D46" t="str">
         <v>weapon</v>
@@ -1874,7 +1874,7 @@
         <v>SSR</v>
       </c>
       <c r="F46" t="str">
-        <v>从星光中窃取力量，化为利刃</v>
+        <v>从邪灵身上剥离紊乱能量化为利刃——你偷的不是它的力量，是它的稳定</v>
       </c>
       <c r="G46" t="str">
         <v>🗡️</v>
@@ -1882,7 +1882,7 @@
       <c r="H46">
         <v>45</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>8</v>
       </c>
     </row>
@@ -1908,13 +1908,13 @@
       <c r="G47" t="str">
         <v>🧥</v>
       </c>
-      <c r="M47">
+      <c r="I47">
         <v>30</v>
       </c>
+      <c r="J47">
+        <v>80</v>
+      </c>
       <c r="N47">
-        <v>80</v>
-      </c>
-      <c r="Q47">
         <v>5</v>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       <c r="H48">
         <v>25</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>0.25</v>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
         <v>SSR</v>
       </c>
       <c r="F49" t="str">
-        <v>偷星者的王冠，暴击时回复5HP</v>
+        <v>偷星者的王冠，暴击时回复5灵能</v>
       </c>
       <c r="G49" t="str">
         <v>👑</v>
@@ -1973,19 +1973,19 @@
         <v>30</v>
       </c>
       <c r="I49">
+        <v>20</v>
+      </c>
+      <c r="J49">
+        <v>50</v>
+      </c>
+      <c r="K49">
         <v>10</v>
       </c>
-      <c r="J49">
+      <c r="L49">
         <v>0.2</v>
       </c>
-      <c r="L49" t="str">
+      <c r="O49" t="str">
         <v>thief_crown</v>
-      </c>
-      <c r="M49">
-        <v>20</v>
-      </c>
-      <c r="N49">
-        <v>50</v>
       </c>
       <c r="S49">
         <v>5</v>
@@ -1999,7 +1999,7 @@
         <v>dark_star_dagger</v>
       </c>
       <c r="C50" t="str">
-        <v>暗星匕首</v>
+        <v>月石匕首</v>
       </c>
       <c r="D50" t="str">
         <v>weapon</v>
@@ -2008,15 +2008,15 @@
         <v>SR</v>
       </c>
       <c r="F50" t="str">
-        <v>暗星铸成的短刃，锋利无声</v>
+        <v>埃及冥界月亮的碎片——锋利得无声</v>
       </c>
       <c r="G50" t="str">
-        <v>🔪</v>
+        <v>🌙</v>
       </c>
       <c r="H50">
         <v>25</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>5</v>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         <v>dark_star_pendant</v>
       </c>
       <c r="C51" t="str">
-        <v>暗星吊坠</v>
+        <v>夜灵吊坠</v>
       </c>
       <c r="D51" t="str">
         <v>accessory</v>
@@ -2037,15 +2037,15 @@
         <v>SR</v>
       </c>
       <c r="F51" t="str">
-        <v>吊坠中闪烁着不祥的光芒</v>
+        <v>灵域夜间逸散的微弱灵光凝结成了坠子</v>
       </c>
       <c r="G51" t="str">
-        <v>📿</v>
+        <v>🌙</v>
       </c>
       <c r="H51">
         <v>15</v>
       </c>
-      <c r="J51">
+      <c r="L51">
         <v>0.1</v>
       </c>
     </row>
@@ -2071,13 +2071,13 @@
       <c r="G52" t="str">
         <v>👢</v>
       </c>
-      <c r="M52">
+      <c r="I52">
         <v>15</v>
       </c>
+      <c r="J52">
+        <v>30</v>
+      </c>
       <c r="N52">
-        <v>30</v>
-      </c>
-      <c r="Q52">
         <v>3</v>
       </c>
     </row>
@@ -2106,10 +2106,10 @@
       <c r="H53">
         <v>12</v>
       </c>
-      <c r="I53">
+      <c r="K53">
         <v>3</v>
       </c>
-      <c r="J53">
+      <c r="L53">
         <v>0.08</v>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>uc_wooden_sword</v>
       </c>
       <c r="C54" t="str">
-        <v>星尘木剑</v>
+        <v>竹简短剑</v>
       </c>
       <c r="D54" t="str">
         <v>weapon</v>
@@ -2130,7 +2130,7 @@
         <v>UC</v>
       </c>
       <c r="F54" t="str">
-        <v>星尘木削成的小剑，比空手好一点</v>
+        <v>竹简之灵凝成的短剑——比空手好一点</v>
       </c>
       <c r="G54" t="str">
         <v>🗡️</v>
@@ -2147,7 +2147,7 @@
         <v>uc_cloth_armor</v>
       </c>
       <c r="C55" t="str">
-        <v>星尘布甲</v>
+        <v>麻布小褂</v>
       </c>
       <c r="D55" t="str">
         <v>armor</v>
@@ -2156,15 +2156,15 @@
         <v>UC</v>
       </c>
       <c r="F55" t="str">
-        <v>星尘编织的布甲，轻便柔软</v>
+        <v>蜀汉城最普通的麻织品——防御聊胜于无</v>
       </c>
       <c r="G55" t="str">
         <v>👕</v>
       </c>
-      <c r="M55">
+      <c r="I55">
         <v>3</v>
       </c>
-      <c r="N55">
+      <c r="J55">
         <v>10</v>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       <c r="G56" t="str">
         <v>💍</v>
       </c>
-      <c r="I56">
+      <c r="K56">
         <v>0.5</v>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>lr_cosmic_cleaver</v>
       </c>
       <c r="C57" t="str">
-        <v>宇宙裂断</v>
+        <v>灵脉裂断</v>
       </c>
       <c r="D57" t="str">
         <v>weapon</v>
@@ -2211,7 +2211,7 @@
         <v>LR</v>
       </c>
       <c r="F57" t="str">
-        <v>劈开宇宙的至高之刃，暴击时30%溅射伤害</v>
+        <v>两条灵脉交叉处锻造的至高之刃——暴击时紊乱能量沿着灵脉溅射</v>
       </c>
       <c r="G57" t="str">
         <v>⚔️</v>
@@ -2219,10 +2219,10 @@
       <c r="H57">
         <v>140</v>
       </c>
-      <c r="I57">
+      <c r="K57">
         <v>25</v>
       </c>
-      <c r="J57">
+      <c r="L57">
         <v>0.6</v>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>lr_event_horizon</v>
       </c>
       <c r="C58" t="str">
-        <v>事件视界</v>
+        <v>灵脉边界</v>
       </c>
       <c r="D58" t="str">
         <v>armor</v>
@@ -2243,15 +2243,15 @@
         <v>LR</v>
       </c>
       <c r="F58" t="str">
-        <v>黑洞边缘的铠甲，受击时10%概率吞噬怪物（Boss无效）</v>
+        <v>灵脉临界点淬成的铠甲——受击时紊乱能量可能反向吞噬来源</v>
       </c>
       <c r="G58" t="str">
         <v>🌀</v>
       </c>
-      <c r="M58">
+      <c r="I58">
         <v>105</v>
       </c>
-      <c r="N58">
+      <c r="J58">
         <v>330</v>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
         <v>lr_nova_core</v>
       </c>
       <c r="C59" t="str">
-        <v>超新星核心</v>
+        <v>灵脉核心</v>
       </c>
       <c r="D59" t="str">
         <v>accessory</v>
@@ -2272,7 +2272,7 @@
         <v>LR</v>
       </c>
       <c r="F59" t="str">
-        <v>超新星碎片，战斗开始触发星爆（200%攻击力全屏伤害）</v>
+        <v>灵脉最深处的共振核心——战斗开始时的星爆是它第一次呼吸</v>
       </c>
       <c r="G59" t="str">
         <v>💫</v>
@@ -2280,10 +2280,10 @@
       <c r="H59">
         <v>40</v>
       </c>
-      <c r="I59">
+      <c r="K59">
         <v>30</v>
       </c>
-      <c r="J59">
+      <c r="L59">
         <v>0.7</v>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
         <v>sp_shooting_star</v>
       </c>
       <c r="C60" t="str">
-        <v>流星光痕</v>
+        <v>陨灵剑</v>
       </c>
       <c r="D60" t="str">
         <v>weapon</v>
@@ -2304,7 +2304,7 @@
         <v>SP</v>
       </c>
       <c r="F60" t="str">
-        <v>攻击留下光痕，5层后触发流星坠落（150%攻击力）</v>
+        <v>陨灵光在你挥过的路径上留下光痕——五层光痕后天空坠下陨击</v>
       </c>
       <c r="G60" t="str">
         <v>🌠</v>
@@ -2312,10 +2312,10 @@
       <c r="H60">
         <v>110</v>
       </c>
-      <c r="I60">
+      <c r="K60">
         <v>18</v>
       </c>
-      <c r="J60">
+      <c r="L60">
         <v>0.45</v>
       </c>
     </row>
@@ -2336,15 +2336,15 @@
         <v>SP</v>
       </c>
       <c r="F61" t="str">
-        <v>每8秒切换元素属性，对应星星分数+20%</v>
+        <v>北欧极光帘幕中剥离的一层——每八秒切换元素属性的共鸣频率</v>
       </c>
       <c r="G61" t="str">
         <v>🌈</v>
       </c>
-      <c r="M61">
+      <c r="I61">
         <v>85</v>
       </c>
-      <c r="N61">
+      <c r="J61">
         <v>260</v>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
         <v>sp_time_hourglass</v>
       </c>
       <c r="C62" t="str">
-        <v>时空沙漏</v>
+        <v>时序沙漏</v>
       </c>
       <c r="D62" t="str">
         <v>accessory</v>
@@ -2365,7 +2365,7 @@
         <v>SP</v>
       </c>
       <c r="F62" t="str">
-        <v>点击星星时5%概率时间回溯，延长战斗3秒</v>
+        <v>时序灵光在沙漏中凝结——不是沙子流过，是战斗延长了</v>
       </c>
       <c r="G62" t="str">
         <v>⏳</v>
@@ -2373,10 +2373,10 @@
       <c r="H62">
         <v>25</v>
       </c>
-      <c r="I62">
+      <c r="K62">
         <v>20</v>
       </c>
-      <c r="J62">
+      <c r="L62">
         <v>0.5</v>
       </c>
     </row>
